--- a/supplementary-material/Supplementary Table S17.xlsx
+++ b/supplementary-material/Supplementary Table S17.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huhuiling/AI_Employment/4 paper：VR WCE/Supplement827/"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3EEE96-F7E5-1A42-BFDF-8A7FC18DE0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>

--- a/supplementary-material/Supplementary Table S17.xlsx
+++ b/supplementary-material/Supplementary Table S17.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3EEE96-F7E5-1A42-BFDF-8A7FC18DE0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A57FFB5-01B4-8344-BA79-EE656BA0803A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="3820" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6380" yWindow="3820" windowWidth="22400" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="kmeans_comparison_summary_segme" sheetId="1" r:id="rId1"/>
@@ -99,40 +99,45 @@
   </si>
   <si>
     <t>kmeans_comparison_summary_segments</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="Helvetica Neue"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="FangSong"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -141,14 +146,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="12"/>
-        <bgColor auto="1"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -275,41 +274,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -439,12 +438,12 @@
     </a:clrScheme>
     <a:fontScheme name="Blank">
       <a:majorFont>
-        <a:latin typeface="Helvetica Neue"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface="Helvetica Neue"/>
         <a:cs typeface="Helvetica Neue"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Helvetica Neue"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface="Helvetica Neue"/>
         <a:cs typeface="Helvetica Neue"/>
       </a:minorFont>
@@ -1442,437 +1441,437 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.3984375" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="1" customWidth="1"/>
-    <col min="2" max="2" width="2.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.33203125" style="1"/>
+    <col min="1" max="1" width="15.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.3984375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="2">
         <v>3</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="3">
         <v>0.56087126928641895</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>34789</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="3">
         <v>23</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="3">
         <v>23</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="3">
         <v>0.90244686104454497</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="6">
         <v>0.53947130211564798</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="6">
         <v>34789</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="6">
         <v>23</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="6">
         <v>23</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="6">
         <v>0.90244686104454497</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="5">
         <v>4</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="6">
         <v>0.33722245119754801</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="6">
         <v>34789</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="6">
         <v>23</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="6">
         <v>23</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="6">
         <v>0.90244686104454497</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="5">
         <v>5</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="6">
         <v>0.25277976136726499</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="6">
         <v>34789</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="6">
         <v>23</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="6">
         <v>23</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="6">
         <v>0.90244686104454497</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="5">
         <v>6</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="6">
         <v>0.24361541931181399</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>34789</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <v>23</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="6">
         <v>23</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="6">
         <v>0.90244686104454497</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="6">
         <v>0.54841204100027796</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="6">
         <v>34789</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="6">
         <v>32</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="6">
         <v>32</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="6">
         <v>0.95357997250997595</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="5">
         <v>2</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="6">
         <v>0.52861126069960596</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>34789</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="6">
         <v>32</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="6">
         <v>32</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="6">
         <v>0.95357997250997595</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="5">
         <v>4</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="6">
         <v>0.32641231899405199</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <v>34789</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="6">
         <v>32</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="6">
         <v>32</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="6">
         <v>0.95357997250997595</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="5">
         <v>5</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="6">
         <v>0.23905946836282099</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="6">
         <v>34789</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="6">
         <v>32</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="6">
         <v>32</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="6">
         <v>0.95357997250997595</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="5">
         <v>6</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="6">
         <v>0.23137287957219599</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <v>34789</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="6">
         <v>32</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="6">
         <v>32</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="6">
         <v>0.95357997250997595</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="5">
         <v>3</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="6">
         <v>0.53854128749629604</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="6">
         <v>34789</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="6">
         <v>88</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="5">
         <v>2</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="6">
         <v>0.52001138755082699</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="6">
         <v>34789</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="6">
         <v>88</v>
       </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
     </row>
-    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="5">
         <v>4</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="6">
         <v>0.31733880376818502</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="6">
         <v>34789</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="6">
         <v>88</v>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="5">
         <v>5</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="6">
         <v>0.23180710289367801</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="6">
         <v>34789</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="6">
         <v>88</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="5">
         <v>6</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="6">
         <v>0.22174715627813699</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="6">
         <v>34789</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="6">
         <v>88</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddFooter>&amp;C&amp;"Calibri,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>